--- a/sources/eddy_step5.xlsx
+++ b/sources/eddy_step5.xlsx
@@ -722,6 +722,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>69fcfb4c-f026-4bd0-86cd-aab7af8a4f9d</t>
+        </is>
+      </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>69fcfb4c-f026-4bd0-86cd-aab7af8a4f9d</t>
@@ -769,6 +774,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>72845d08-c01c-4c2e-b9bb-eb6bf7061e42</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>72845d08-c01c-4c2e-b9bb-eb6bf7061e42</t>
@@ -814,6 +824,11 @@
       <c r="M8" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>89b9a62a-0e17-41f7-9bcd-95c83f81b48a</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -10131,6 +10146,11 @@
           <t>mmmhhmmmhmmm</t>
         </is>
       </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>75dc99c7-8cb7-47d7-b907-7045f1e2dcd1</t>
+        </is>
+      </c>
       <c r="Q184" t="inlineStr">
         <is>
           <t>75dc99c7-8cb7-47d7-b907-7045f1e2dcd1</t>
@@ -10163,6 +10183,11 @@
           <t>mmmhhL</t>
         </is>
       </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>daff2cc0-5de1-450f-b06c-c4e7db7f803b</t>
+        </is>
+      </c>
       <c r="Q185" t="inlineStr">
         <is>
           <t>daff2cc0-5de1-450f-b06c-c4e7db7f803b</t>
@@ -10178,6 +10203,11 @@
       <c r="A186" t="inlineStr">
         <is>
           <t>– Leg Whip Series</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>b321b883-5528-4383-9e3a-01d93e60f6ab</t>
         </is>
       </c>
       <c r="Q186" t="inlineStr">
